--- a/output/stock_quant_scores/EQR_income_df.xlsx
+++ b/output/stock_quant_scores/EQR_income_df.xlsx
@@ -1417,7 +1417,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1673495000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1430,7 +1432,9 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>3.56</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>34010000</v>
@@ -1438,7 +1442,9 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>1332850000</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
@@ -1478,9 +1484,13 @@
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>1515205000</v>
+      </c>
       <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>2463997000</v>
+      </c>
       <c r="BG6" t="inlineStr"/>
     </row>
   </sheetData>
